--- a/results/Int Task Remove ACC 0.1/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_5_permute.xlsx
@@ -440,637 +440,637 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7670027341079972</v>
+        <v>0.7404875825928458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7610218728639782</v>
+        <v>0.751224652540442</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7660059239006607</v>
+        <v>0.7489747095010253</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7474367737525632</v>
+        <v>0.75580997949419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7537024379129642</v>
+        <v>0.7428229665071771</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7533891547049442</v>
+        <v>0.7417122351332878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7533891547049442</v>
+        <v>0.7417122351332878</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7548131692868535</v>
+        <v>0.7421109592162224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7656641604010025</v>
+        <v>0.7397186147186148</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7705342902711323</v>
+        <v>0.7416267942583732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7752335383914331</v>
+        <v>0.7448735475051265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7828662565504672</v>
+        <v>0.7438197767145136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7828662565504672</v>
+        <v>0.6354522670312144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7710754158122579</v>
+        <v>0.6354522670312144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7555821371610846</v>
+        <v>0.6419457735247209</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7491740715424926</v>
+        <v>0.64761335156072</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6758088402825245</v>
+        <v>0.6433982683982684</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.667179311916154</v>
+        <v>0.6415755297334245</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6516290726817042</v>
+        <v>0.6254272043745728</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6516290726817042</v>
+        <v>0.6312941444520392</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6490943267259057</v>
+        <v>0.6312941444520392</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6478981544771019</v>
+        <v>0.5945260879471406</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6469583048530416</v>
+        <v>0.5702608794714058</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6442811574390521</v>
+        <v>0.5666154021417179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6478127136021873</v>
+        <v>0.5471348826611985</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6490088858509911</v>
+        <v>0.546451355661882</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6527398040555936</v>
+        <v>0.5382205513784462</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.64149008885851</v>
+        <v>0.5366256550467077</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5404420141262246</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6609990886306676</v>
+        <v>0.543090681248576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6619958988380041</v>
+        <v>0.5771531100478469</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6605434039644567</v>
+        <v>0.5831339712918659</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6276771474139895</v>
+        <v>0.557615629984051</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6233481430849852</v>
+        <v>0.6201013898382319</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6233481430849852</v>
+        <v>0.6323479152426521</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6218671679197996</v>
+        <v>0.6323479152426521</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6345693779904307</v>
+        <v>0.538192071086808</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6345693779904307</v>
+        <v>0.5452267031214399</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6521701982228298</v>
+        <v>0.5266575529733425</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6039815447710185</v>
+        <v>0.5408692185007975</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5928172704488495</v>
+        <v>0.4885509227614491</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6014752791068581</v>
+        <v>0.5218728639781272</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6008771929824561</v>
+        <v>0.5344611528822055</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5835611756664388</v>
+        <v>0.5377648667122351</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5876338573706995</v>
+        <v>0.5366256550467077</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5876338573706995</v>
+        <v>0.5366256550467077</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5818808384597858</v>
+        <v>0.5342048302574618</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5740772385509227</v>
+        <v>0.5371952608794714</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5674982911825017</v>
+        <v>0.5360845295055822</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5681248575985418</v>
+        <v>0.5255753018910914</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5687514240145819</v>
+        <v>0.5474481658692185</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5682672590567328</v>
+        <v>0.4512987012987013</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5369104579630896</v>
+        <v>0.455684666210982</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5679254955570745</v>
+        <v>0.4628047391205286</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5671565276828434</v>
+        <v>0.4571371610845295</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5674128503075871</v>
+        <v>0.4536056049213944</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4975791752107542</v>
+        <v>0.4548017771701982</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5079175210754158</v>
+        <v>0.4628901799954432</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.512218045112782</v>
+        <v>0.4696969696969697</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5131009341535657</v>
+        <v>0.4696969696969697</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.516660970608339</v>
+        <v>0.4716621098200046</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5224709501025291</v>
+        <v>0.4735418090681249</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5158350421508316</v>
+        <v>0.4705798587377535</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5290498974709501</v>
+        <v>0.4687856003645477</v>
       </c>
     </row>
     <row r="66">
@@ -1080,247 +1080,247 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5272841193893826</v>
+        <v>0.4669059011164274</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5233823194349511</v>
+        <v>0.4672191843244475</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5179141034404192</v>
+        <v>0.4699532923217133</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5243791296422875</v>
+        <v>0.4726874003189793</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5280530872636136</v>
+        <v>0.4723741171109592</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5428628389154705</v>
+        <v>0.486699703804967</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4850478468899522</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5118478013214856</v>
+        <v>0.4844212804739121</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5223570289359762</v>
+        <v>0.4943893825472773</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4986614262930052</v>
+        <v>0.496639325586694</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4925666438824334</v>
+        <v>0.496639325586694</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.496183640920483</v>
+        <v>0.4963260423786739</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4932501708817498</v>
+        <v>0.4951583504215084</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4886648439280019</v>
+        <v>0.4951583504215084</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.493591934381408</v>
+        <v>0.4947596263385737</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4912280701754386</v>
+        <v>0.4940476190476191</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4913989519252677</v>
+        <v>0.4965538847117795</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.493421052631579</v>
+        <v>0.4968671679197995</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4969810890863522</v>
+        <v>0.4971804511278196</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4974367737525632</v>
+        <v>0.4994588744588745</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4984620642515379</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4998860788334473</v>
+        <v>0.4997721576668945</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4989177489177489</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5027910685805422</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5027341079972659</v>
+        <v>0.4993734335839599</v>
       </c>
     </row>
   </sheetData>
